--- a/Día 5/Mayúsculas+y+Minúsculas.xlsx
+++ b/Día 5/Mayúsculas+y+Minúsculas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Día 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F44ACF4-10D6-4DBE-B23B-30989EB68210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E79F29C-20EE-4BC4-9EC2-7017E9CE9D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E13B40F4-CC2C-479E-87C3-FC61E28B174A}"/>
   </bookViews>
@@ -101,15 +101,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -177,13 +177,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,25 +506,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="2:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
@@ -600,8 +600,15 @@
         <v>Nuestro hotel abre sus puertas</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="str">
+        <f>UPPER(B2)</f>
+        <v>NUESTRO HOTEL ABRE SUS PUERTAS</v>
+      </c>
+      <c r="D17" t="str">
+        <f>UPPER(LEFT(B2,1))&amp;LOWER(RIGHT(B2,LEN(B2)-1))</f>
+        <v>Nuestro hotel abre sus puertas</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -609,5 +616,6 @@
     <mergeCell ref="E2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>